--- a/assets/template/template_excel.xlsx
+++ b/assets/template/template_excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Computer\Project\laporan_bsc-main\assets\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F303401B-CDF1-47E9-A586-25BB648BDB47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A41C77DC-5E16-4A25-98B8-348C38F2AA92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{694369AE-DBA1-4A1F-BF57-5BE6D69646E2}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="228">
   <si>
     <t>NO</t>
   </si>
@@ -732,6 +732,15 @@
   </si>
   <si>
     <t>$subTotal_414_B</t>
+  </si>
+  <si>
+    <t>$skor_412_Total</t>
+  </si>
+  <si>
+    <t>$skor_413_Total</t>
+  </si>
+  <si>
+    <t>$skor_414_Total</t>
   </si>
 </sst>
 </file>
@@ -940,18 +949,24 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -963,12 +978,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1319,10 +1328,10 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="36"/>
+      <c r="B1" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="30"/>
       <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
@@ -1345,7 +1354,7 @@
         <f>D4</f>
         <v>20</v>
       </c>
-      <c r="E2" s="37">
+      <c r="E2" s="28">
         <f>IF(ISTEXT(E3),0,E3)</f>
         <v>0</v>
       </c>
@@ -1355,10 +1364,10 @@
       <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="30"/>
+      <c r="C3" s="29"/>
       <c r="D3" s="1"/>
       <c r="E3" s="6" t="s">
         <v>137</v>
@@ -1369,10 +1378,10 @@
       <c r="A4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="30" t="s">
+      <c r="B4" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="30"/>
+      <c r="C4" s="29"/>
       <c r="D4" s="1">
         <f>SUM(D5:D15)</f>
         <v>20</v>
@@ -1578,7 +1587,7 @@
         <f>D19+D30</f>
         <v>30</v>
       </c>
-      <c r="E17" s="37">
+      <c r="E17" s="28">
         <f>IF(ISTEXT(E18),0,E18)</f>
         <v>0</v>
       </c>
@@ -1588,10 +1597,10 @@
       <c r="A18" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B18" s="30" t="s">
+      <c r="B18" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="30"/>
+      <c r="C18" s="29"/>
       <c r="D18" s="1"/>
       <c r="E18" s="6" t="s">
         <v>150</v>
@@ -1602,10 +1611,10 @@
       <c r="A19" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B19" s="30" t="s">
+      <c r="B19" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="C19" s="30"/>
+      <c r="C19" s="29"/>
       <c r="D19" s="1">
         <f>SUM(D20:D28)</f>
         <v>12</v>
@@ -1771,10 +1780,10 @@
       <c r="A30" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B30" s="30" t="s">
+      <c r="B30" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="C30" s="30"/>
+      <c r="C30" s="29"/>
       <c r="D30" s="1">
         <f>SUM(D31:D41)</f>
         <v>18</v>
@@ -1980,7 +1989,7 @@
         <f>D45+D63+D73+D81+D84</f>
         <v>30</v>
       </c>
-      <c r="E43" s="37">
+      <c r="E43" s="28">
         <f>IF(ISTEXT(E44),0,E44)</f>
         <v>0</v>
       </c>
@@ -1990,10 +1999,10 @@
       <c r="A44" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B44" s="30" t="s">
+      <c r="B44" s="29" t="s">
         <v>60</v>
       </c>
-      <c r="C44" s="30"/>
+      <c r="C44" s="29"/>
       <c r="D44" s="1"/>
       <c r="E44" s="6" t="s">
         <v>173</v>
@@ -2004,10 +2013,10 @@
       <c r="A45" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B45" s="30" t="s">
+      <c r="B45" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="C45" s="30"/>
+      <c r="C45" s="29"/>
       <c r="D45" s="1">
         <f>SUM(D46:D61)</f>
         <v>16</v>
@@ -2285,10 +2294,10 @@
       <c r="A63" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="B63" s="30" t="s">
+      <c r="B63" s="29" t="s">
         <v>85</v>
       </c>
-      <c r="C63" s="30"/>
+      <c r="C63" s="29"/>
       <c r="D63" s="1">
         <f>SUM(D64:D71)</f>
         <v>6</v>
@@ -2438,10 +2447,10 @@
       <c r="A73" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="B73" s="30" t="s">
+      <c r="B73" s="29" t="s">
         <v>95</v>
       </c>
-      <c r="C73" s="30"/>
+      <c r="C73" s="29"/>
       <c r="D73" s="1">
         <f>SUM(D74:D79)</f>
         <v>6</v>
@@ -2559,10 +2568,10 @@
       <c r="A81" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="B81" s="30" t="s">
+      <c r="B81" s="29" t="s">
         <v>103</v>
       </c>
-      <c r="C81" s="30"/>
+      <c r="C81" s="29"/>
       <c r="D81" s="1">
         <f>SUM(D82)</f>
         <v>1</v>
@@ -2600,10 +2609,10 @@
       <c r="A84" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="B84" s="30" t="s">
+      <c r="B84" s="29" t="s">
         <v>106</v>
       </c>
-      <c r="C84" s="30"/>
+      <c r="C84" s="29"/>
       <c r="D84" s="1">
         <v>1</v>
       </c>
@@ -2624,15 +2633,15 @@
       <c r="A86" s="4">
         <v>4</v>
       </c>
-      <c r="B86" s="30" t="s">
+      <c r="B86" s="29" t="s">
         <v>107</v>
       </c>
-      <c r="C86" s="30"/>
+      <c r="C86" s="29"/>
       <c r="D86" s="1">
         <f>D88+D95+D99+D103</f>
         <v>20</v>
       </c>
-      <c r="E86" s="37">
+      <c r="E86" s="28">
         <f>IF(ISTEXT(E87),0,E87)</f>
         <v>0</v>
       </c>
@@ -2642,10 +2651,10 @@
       <c r="A87" s="26" t="s">
         <v>210</v>
       </c>
-      <c r="B87" s="30" t="s">
+      <c r="B87" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="C87" s="30"/>
+      <c r="C87" s="29"/>
       <c r="D87" s="27"/>
       <c r="E87" s="6" t="s">
         <v>212</v>
@@ -2770,7 +2779,7 @@
         <v>4</v>
       </c>
       <c r="E95" s="6" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="F95" s="12"/>
     </row>
@@ -2818,16 +2827,16 @@
       <c r="A99" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="B99" s="30" t="s">
+      <c r="B99" s="29" t="s">
         <v>120</v>
       </c>
-      <c r="C99" s="30"/>
+      <c r="C99" s="29"/>
       <c r="D99" s="1">
         <f>SUM(D100:D101)</f>
         <v>4</v>
       </c>
       <c r="E99" s="6" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="F99" s="12"/>
     </row>
@@ -2884,7 +2893,7 @@
         <v>4</v>
       </c>
       <c r="E103" s="6" t="s">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="F103" s="12"/>
     </row>
@@ -2921,9 +2930,9 @@
       <c r="F105" s="5"/>
     </row>
     <row r="106" spans="1:6" ht="24.6" customHeight="1">
-      <c r="A106" s="32"/>
-      <c r="B106" s="33"/>
-      <c r="C106" s="34"/>
+      <c r="A106" s="34"/>
+      <c r="B106" s="35"/>
+      <c r="C106" s="36"/>
       <c r="D106" s="1">
         <f>D2+D17+D43+D86</f>
         <v>100</v>
@@ -2950,10 +2959,10 @@
       <c r="A109" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B109" s="35" t="s">
+      <c r="B109" s="37" t="s">
         <v>128</v>
       </c>
-      <c r="C109" s="35"/>
+      <c r="C109" s="37"/>
       <c r="D109" s="22" t="s">
         <v>129</v>
       </c>
@@ -2965,10 +2974,10 @@
       <c r="A110" s="22">
         <v>1</v>
       </c>
-      <c r="B110" s="28" t="s">
+      <c r="B110" s="32" t="s">
         <v>131</v>
       </c>
-      <c r="C110" s="28"/>
+      <c r="C110" s="32"/>
       <c r="D110" s="22">
         <v>20</v>
       </c>
@@ -2981,10 +2990,10 @@
       <c r="A111" s="22">
         <v>2</v>
       </c>
-      <c r="B111" s="28" t="s">
+      <c r="B111" s="32" t="s">
         <v>132</v>
       </c>
-      <c r="C111" s="28"/>
+      <c r="C111" s="32"/>
       <c r="D111" s="22">
         <v>30</v>
       </c>
@@ -2997,10 +3006,10 @@
       <c r="A112" s="22">
         <v>3</v>
       </c>
-      <c r="B112" s="28" t="s">
+      <c r="B112" s="32" t="s">
         <v>133</v>
       </c>
-      <c r="C112" s="28"/>
+      <c r="C112" s="32"/>
       <c r="D112" s="22">
         <v>30</v>
       </c>
@@ -3013,10 +3022,10 @@
       <c r="A113" s="22">
         <v>4</v>
       </c>
-      <c r="B113" s="28" t="s">
+      <c r="B113" s="32" t="s">
         <v>134</v>
       </c>
-      <c r="C113" s="28"/>
+      <c r="C113" s="32"/>
       <c r="D113" s="22">
         <v>20</v>
       </c>
@@ -3027,10 +3036,10 @@
     </row>
     <row r="114" spans="1:5" ht="19.95" customHeight="1">
       <c r="A114" s="7"/>
-      <c r="B114" s="29" t="s">
+      <c r="B114" s="33" t="s">
         <v>135</v>
       </c>
-      <c r="C114" s="29"/>
+      <c r="C114" s="33"/>
       <c r="D114" s="24">
         <f>SUM(D110:D113)</f>
         <v>100</v>
@@ -3054,12 +3063,15 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="A106:C106"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="B111:C111"/>
     <mergeCell ref="B95:C95"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B30:C30"/>
@@ -3073,15 +3085,12 @@
     <mergeCell ref="B86:C86"/>
     <mergeCell ref="B88:C88"/>
     <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="B113:C113"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="B103:C103"/>
-    <mergeCell ref="A106:C106"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="B110:C110"/>
-    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B17:C17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
